--- a/artfynd/A 57760-2025 artfynd.xlsx
+++ b/artfynd/A 57760-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118991</v>
       </c>
       <c r="B2" t="n">
-        <v>57805</v>
+        <v>57807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57760-2025 artfynd.xlsx
+++ b/artfynd/A 57760-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118991</v>
       </c>
       <c r="B2" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57760-2025 artfynd.xlsx
+++ b/artfynd/A 57760-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118991</v>
       </c>
       <c r="B2" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57760-2025 artfynd.xlsx
+++ b/artfynd/A 57760-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118991</v>
       </c>
       <c r="B2" t="n">
-        <v>57809</v>
+        <v>57812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57760-2025 artfynd.xlsx
+++ b/artfynd/A 57760-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118991</v>
       </c>
       <c r="B2" t="n">
-        <v>57812</v>
+        <v>57813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
